--- a/Data point Supporting files/Germany 2021/Reserves.xlsx
+++ b/Data point Supporting files/Germany 2021/Reserves.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="24"/>
   </bookViews>
   <sheets>
     <sheet name="Aluminium" sheetId="1" state="visible" r:id="rId2"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="146">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -743,61 +743,61 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="10.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>450</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>560</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>580</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>250</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <f aca="false">SUM(B2:B6)</f>
         <v>11840</v>
       </c>
@@ -2532,7 +2532,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2543,12 +2543,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>6800000</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="1" t="n">
-        <v>360000</v>
+      <c r="B3" s="1" t="n">
+        <v>6800000</v>
       </c>
     </row>
   </sheetData>
@@ -2567,7 +2575,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2592,6 +2600,14 @@
       </c>
       <c r="B3" s="1" t="n">
         <v>40000</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>134000</v>
       </c>
     </row>
   </sheetData>
